--- a/xlsx/Power/p15.xlsx
+++ b/xlsx/Power/p15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0B7595-2286-47FF-9C5D-9A40CE8EB32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468B6573-1721-4D64-819C-165CDB4D807E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{A4C00549-8BC7-477B-8348-58740D06843B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{A4C00549-8BC7-477B-8348-58740D06843B}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="C1">
-        <v>0.247</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D1">
-        <v>0.32400000000000001</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="E1">
-        <v>0.38900000000000001</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="F1">
-        <v>0.504</v>
+        <v>0.251</v>
       </c>
       <c r="G1">
-        <v>0.60099999999999998</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="H1">
-        <v>0.66500000000000004</v>
+        <v>0.441</v>
       </c>
       <c r="I1">
-        <v>0.72299999999999998</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="J1">
-        <v>0.78700000000000003</v>
+        <v>0.63600000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.108</v>
       </c>
       <c r="C2">
-        <v>0.215</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D2">
-        <v>0.27300000000000002</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="E2">
-        <v>0.33700000000000002</v>
+        <v>0.108</v>
       </c>
       <c r="F2">
-        <v>0.434</v>
+        <v>0.217</v>
       </c>
       <c r="G2">
-        <v>0.51400000000000001</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="H2">
-        <v>0.57599999999999996</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="I2">
-        <v>0.63500000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="J2">
-        <v>0.70699999999999996</v>
+        <v>0.55500000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.112</v>
       </c>
       <c r="C3">
-        <v>0.188</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="D3">
-        <v>0.25600000000000001</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="E3">
-        <v>0.29699999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="F3">
-        <v>0.36</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="G3">
-        <v>0.45300000000000001</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="H3">
-        <v>0.48499999999999999</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="I3">
-        <v>0.56000000000000005</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="J3">
-        <v>0.58799999999999997</v>
+        <v>0.59299999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B4">
-        <v>0.104</v>
+        <v>0.113</v>
       </c>
       <c r="C4">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="D4">
-        <v>0.224</v>
+        <v>0.218</v>
       </c>
       <c r="E4">
-        <v>0.25700000000000001</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="F4">
-        <v>0.30499999999999999</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="G4">
-        <v>0.36499999999999999</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="H4">
-        <v>0.39200000000000002</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="I4">
-        <v>0.46300000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J4">
-        <v>0.49199999999999999</v>
+        <v>0.49399999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.106</v>
       </c>
       <c r="C6">
-        <v>0.183</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="D6">
-        <v>0.20699999999999999</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="E6">
-        <v>0.246</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="F6">
-        <v>0.34399999999999997</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="G6">
-        <v>0.39600000000000002</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="H6">
-        <v>0.44400000000000001</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="I6">
-        <v>0.51700000000000002</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="J6">
-        <v>0.56100000000000005</v>
+        <v>0.58699999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.107</v>
       </c>
       <c r="C7">
-        <v>0.17499999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="D7">
-        <v>0.20699999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="E7">
-        <v>0.23599999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="F7">
-        <v>0.32400000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="G7">
-        <v>0.374</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="H7">
         <v>0.40600000000000003</v>
       </c>
       <c r="I7">
-        <v>0.47199999999999998</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="J7">
-        <v>0.52300000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="C8">
-        <v>0.16700000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.20499999999999999</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E8">
-        <v>0.252</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="F8">
-        <v>0.29899999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G8">
-        <v>0.31900000000000001</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="H8">
-        <v>0.35399999999999998</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="I8">
-        <v>0.49199999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="J8">
-        <v>0.50700000000000001</v>
+        <v>5.6000000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="C9">
-        <v>3.7999999999999999E-2</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="D9">
-        <v>6.9000000000000006E-2</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="E9">
-        <v>0.105</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="F9">
-        <v>0.121</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="G9">
-        <v>0.155</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="H9">
-        <v>0.17499999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="I9">
-        <v>0.191</v>
+        <v>0.215</v>
       </c>
       <c r="J9">
-        <v>0.216</v>
+        <v>0.23799999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p15.xlsx
+++ b/xlsx/Power/p15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468B6573-1721-4D64-819C-165CDB4D807E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C670C3BE-670A-4137-B880-291E7AF30E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{A4C00549-8BC7-477B-8348-58740D06843B}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{A4C00549-8BC7-477B-8348-58740D06843B}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="C1">
-        <v>8.0000000000000002E-3</v>
+        <v>0.247</v>
       </c>
       <c r="D1">
-        <v>5.0999999999999997E-2</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="E1">
-        <v>0.11799999999999999</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="F1">
-        <v>0.251</v>
+        <v>0.504</v>
       </c>
       <c r="G1">
-        <v>0.34300000000000003</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="H1">
-        <v>0.441</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="I1">
-        <v>0.53300000000000003</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="J1">
-        <v>0.63600000000000001</v>
+        <v>0.78700000000000003</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.108</v>
       </c>
       <c r="C2">
-        <v>8.0000000000000002E-3</v>
+        <v>0.215</v>
       </c>
       <c r="D2">
-        <v>4.8000000000000001E-2</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="E2">
-        <v>0.108</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="F2">
-        <v>0.217</v>
+        <v>0.434</v>
       </c>
       <c r="G2">
-        <v>0.29899999999999999</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="H2">
-        <v>0.36699999999999999</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="I2">
-        <v>0.47</v>
+        <v>0.63500000000000001</v>
       </c>
       <c r="J2">
-        <v>0.55500000000000005</v>
+        <v>0.70699999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.112</v>
       </c>
       <c r="C3">
-        <v>0.23400000000000001</v>
+        <v>0.188</v>
       </c>
       <c r="D3">
-        <v>0.26700000000000002</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="E3">
-        <v>0.307</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="F3">
-        <v>0.36699999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="G3">
-        <v>0.45400000000000001</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="H3">
-        <v>0.49199999999999999</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="I3">
-        <v>0.56200000000000006</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J3">
-        <v>0.59299999999999997</v>
+        <v>0.58799999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="B4">
-        <v>0.113</v>
+        <v>0.104</v>
       </c>
       <c r="C4">
-        <v>0.159</v>
+        <v>0.156</v>
       </c>
       <c r="D4">
-        <v>0.218</v>
+        <v>0.224</v>
       </c>
       <c r="E4">
-        <v>0.25800000000000001</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="F4">
-        <v>0.30599999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="G4">
-        <v>0.36399999999999999</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H4">
-        <v>0.38900000000000001</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="I4">
-        <v>0.46200000000000002</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="J4">
-        <v>0.49399999999999999</v>
+        <v>0.49199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.106</v>
       </c>
       <c r="C6">
-        <v>0.33500000000000002</v>
+        <v>0.183</v>
       </c>
       <c r="D6">
-        <v>0.27100000000000002</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="E6">
-        <v>0.29799999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="F6">
-        <v>0.36799999999999999</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="G6">
-        <v>0.41199999999999998</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="H6">
-        <v>0.45900000000000002</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="I6">
-        <v>0.53100000000000003</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="J6">
-        <v>0.58699999999999997</v>
+        <v>0.56100000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.107</v>
       </c>
       <c r="C7">
-        <v>0.17199999999999999</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="D7">
-        <v>0.20599999999999999</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="E7">
-        <v>0.23699999999999999</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="F7">
-        <v>0.32</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="G7">
-        <v>0.36199999999999999</v>
+        <v>0.374</v>
       </c>
       <c r="H7">
         <v>0.40600000000000003</v>
       </c>
       <c r="I7">
-        <v>0.46600000000000003</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="J7">
-        <v>0.51800000000000002</v>
+        <v>0.52300000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="D8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="E8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.252</v>
       </c>
       <c r="F8">
-        <v>0.1</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="G8">
-        <v>0.13900000000000001</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="H8">
-        <v>0.18099999999999999</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="I8">
-        <v>5.5E-2</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="J8">
-        <v>5.6000000000000001E-2</v>
+        <v>0.50700000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="C9">
-        <v>0.23300000000000001</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="D9">
-        <v>0.80800000000000005</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E9">
-        <v>0.60299999999999998</v>
+        <v>0.105</v>
       </c>
       <c r="F9">
-        <v>0.24399999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="G9">
-        <v>0.22600000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="H9">
-        <v>0.20899999999999999</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="I9">
-        <v>0.215</v>
+        <v>0.191</v>
       </c>
       <c r="J9">
-        <v>0.23799999999999999</v>
+        <v>0.216</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p15.xlsx
+++ b/xlsx/Power/p15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C670C3BE-670A-4137-B880-291E7AF30E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07538E13-069B-4F19-AB48-019E7036F699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{A4C00549-8BC7-477B-8348-58740D06843B}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{A4C00549-8BC7-477B-8348-58740D06843B}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,16 +404,16 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="C1">
-        <v>0.247</v>
+        <v>0.248</v>
       </c>
       <c r="D1">
-        <v>0.32400000000000001</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="E1">
-        <v>0.38900000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="F1">
-        <v>0.504</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="G1">
         <v>0.60099999999999998</v>
@@ -422,10 +422,10 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="I1">
-        <v>0.72299999999999998</v>
+        <v>0.72899999999999998</v>
       </c>
       <c r="J1">
-        <v>0.78700000000000003</v>
+        <v>0.79400000000000004</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -433,132 +433,132 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="B2">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="C2">
-        <v>0.215</v>
+        <v>0.217</v>
       </c>
       <c r="D2">
         <v>0.27300000000000002</v>
       </c>
       <c r="E2">
-        <v>0.33700000000000002</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="F2">
-        <v>0.434</v>
+        <v>0.432</v>
       </c>
       <c r="G2">
-        <v>0.51400000000000001</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="H2">
-        <v>0.57599999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I2">
-        <v>0.63500000000000001</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="J2">
-        <v>0.70699999999999996</v>
+        <v>0.71099999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>7.9000000000000001E-2</v>
+        <v>7.8E-2</v>
       </c>
       <c r="B3">
-        <v>0.112</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="C3">
-        <v>0.188</v>
+        <v>0.192</v>
       </c>
       <c r="D3">
         <v>0.25600000000000001</v>
       </c>
       <c r="E3">
-        <v>0.29699999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="F3">
-        <v>0.36</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="G3">
-        <v>0.45300000000000001</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="H3">
-        <v>0.48499999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="I3">
-        <v>0.56000000000000005</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="J3">
-        <v>0.58799999999999997</v>
+        <v>0.59899999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.08</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="B4">
-        <v>0.104</v>
+        <v>0.107</v>
       </c>
       <c r="C4">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="D4">
-        <v>0.224</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="E4">
-        <v>0.25700000000000001</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="F4">
-        <v>0.30499999999999999</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="G4">
-        <v>0.36499999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H4">
-        <v>0.39200000000000002</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="I4">
-        <v>0.46300000000000002</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="J4">
-        <v>0.49199999999999999</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7.1999999999999995E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="B6">
         <v>0.106</v>
@@ -567,48 +567,48 @@
         <v>0.183</v>
       </c>
       <c r="D6">
-        <v>0.20699999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="E6">
-        <v>0.246</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="F6">
-        <v>0.34399999999999997</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="G6">
-        <v>0.39600000000000002</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="H6">
-        <v>0.44400000000000001</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I6">
-        <v>0.51700000000000002</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="J6">
-        <v>0.56100000000000005</v>
+        <v>0.56799999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6.9000000000000006E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="B7">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="C7">
-        <v>0.17499999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="D7">
-        <v>0.20699999999999999</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="E7">
-        <v>0.23599999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="F7">
-        <v>0.32400000000000001</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="G7">
-        <v>0.374</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="H7">
         <v>0.40600000000000003</v>
@@ -617,7 +617,7 @@
         <v>0.47199999999999998</v>
       </c>
       <c r="J7">
-        <v>0.52300000000000002</v>
+        <v>0.52200000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -634,19 +634,19 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="E8">
-        <v>0.252</v>
+        <v>0.255</v>
       </c>
       <c r="F8">
-        <v>0.29799999999999999</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="G8">
-        <v>0.31900000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="H8">
         <v>0.35399999999999998</v>
       </c>
       <c r="I8">
-        <v>0.48899999999999999</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="J8">
         <v>0.50700000000000001</v>
@@ -657,7 +657,7 @@
         <v>0.06</v>
       </c>
       <c r="B9">
-        <v>9.2999999999999999E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="C9">
         <v>3.7999999999999999E-2</v>
@@ -666,22 +666,22 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="E9">
-        <v>0.105</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="F9">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="G9">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="H9">
-        <v>0.17499999999999999</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="I9">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="J9">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
     </row>
   </sheetData>
